--- a/Assets/Lion/Weapon/Game Data/Level/Excel/Weapon_11.xlsx
+++ b/Assets/Lion/Weapon/Game Data/Level/Excel/Weapon_11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vantan\Lion\Assets\Lion\Weapon\Game Data\Level\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D041F7A-0B0B-4EDD-A1B0-1BF222948D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901FEE27-2EDD-4ADF-96DE-0737225383E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,7 +434,9 @@
       <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
@@ -4352,7 +4354,9 @@
       <c r="E121" s="1">
         <v>3</v>
       </c>
-      <c r="F121" s="1"/>
+      <c r="F121" s="1">
+        <v>0</v>
+      </c>
       <c r="G121" s="1">
         <v>10</v>
       </c>
